--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -10782,7 +10782,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市定州市保定定州万达</t>
+          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
+          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
+          <t>小米汽车河北省保定市定州市保定定州万达</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
+          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市集美区集美汽车城</t>
+          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市集美区天水路503号</t>
+          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
+          <t>小米汽车福建省厦门市集美区集美汽车城</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
+          <t>福建省厦门市集美区天水路503号</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12485,22 +12485,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12510,29 +12510,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
+          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12542,29 +12542,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12574,29 +12574,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
+          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12606,29 +12606,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
+          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
         </is>
       </c>
     </row>
@@ -12650,17 +12650,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
@@ -12709,22 +12709,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12734,29 +12734,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
+          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
         </is>
       </c>
     </row>
@@ -12805,22 +12805,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12830,29 +12830,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
@@ -12874,17 +12874,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12894,29 +12894,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
+          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
+          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
         </is>
       </c>
     </row>
@@ -12965,22 +12965,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>马鞍山雨山万达广场</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
+          <t>马鞍山雨山万达广场城市展厅1号门</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12997,22 +12997,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台龙口保利</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（龙口保利广场）</t>
+          <t>小鹏汽车九江九瑞大道销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13029,22 +13029,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场</t>
+          <t>华为智能生活馆•烟台龙口保利</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场城市展厅1号门</t>
+          <t>华为授权体验店（龙口保利广场）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13061,22 +13061,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江九瑞大道销售服务中心</t>
+          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13098,17 +13098,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区万达广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13118,14 +13118,14 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -13135,12 +13135,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>华为授权体验店（济南新辰天地）</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -13189,22 +13189,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>小米汽车四川省绵阳市涪城区万达广场</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（济南新辰天地）</t>
+          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -10782,7 +10782,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
+          <t>小米汽车河北省保定市定州市保定定州万达</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
+          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市定州市保定定州万达</t>
+          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
+          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
+          <t>小米汽车福建省厦门市集美区集美汽车城</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
+          <t>福建省厦门市集美区天水路503号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市集美区集美汽车城</t>
+          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市集美区天水路503号</t>
+          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司</t>
+          <t>南京利之星汽车销售服务有限公司河西分公司</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -11939,12 +11939,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>栖霞区仙尧路9号</t>
+          <t>鼓楼区汉中门大街309号B栋一层</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 17 期</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司河西分公司</t>
+          <t>南京利之星汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11971,12 +11971,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>鼓楼区汉中门大街309号B栋一层</t>
+          <t>栖霞区仙尧路9号</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期</t>
+          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12517,22 +12517,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
         </is>
       </c>
     </row>
@@ -12613,22 +12613,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12638,29 +12638,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12670,29 +12670,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
+          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
         </is>
       </c>
     </row>
@@ -12714,17 +12714,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
+          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
         </is>
       </c>
     </row>
@@ -12773,22 +12773,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12798,29 +12798,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
+          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
+          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
         </is>
       </c>
     </row>
@@ -12842,17 +12842,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
         </is>
       </c>
     </row>
@@ -12901,22 +12901,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
@@ -12965,22 +12965,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场</t>
+          <t>华为智能生活馆•烟台龙口保利</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场城市展厅1号门</t>
+          <t>华为授权体验店（龙口保利广场）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12997,22 +12997,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江九瑞大道销售服务中心</t>
+          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13029,22 +13029,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台龙口保利</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（龙口保利广场）</t>
+          <t>小鹏汽车九江九瑞大道销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13061,22 +13061,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>马鞍山雨山万达广场</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
+          <t>马鞍山雨山万达广场城市展厅1号门</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -10782,7 +10782,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市定州市保定定州万达</t>
+          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
+          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
+          <t>小米汽车河北省保定市定州市保定定州万达</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
+          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -12485,22 +12485,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12510,29 +12510,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
+          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12542,29 +12542,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12574,14 +12574,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
+          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12606,29 +12606,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
+          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12638,29 +12638,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
         </is>
       </c>
     </row>
@@ -12741,22 +12741,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12766,29 +12766,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12798,29 +12798,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12830,29 +12830,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
+          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
+          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
         </is>
       </c>
     </row>
@@ -12874,17 +12874,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12894,29 +12894,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
+          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
         </is>
       </c>
     </row>
@@ -12965,22 +12965,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台龙口保利</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（龙口保利广场）</t>
+          <t>小鹏汽车九江九瑞大道销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12997,22 +12997,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>马鞍山雨山万达广场</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
+          <t>马鞍山雨山万达广场城市展厅1号门</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13029,22 +13029,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江九瑞大道销售服务中心</t>
+          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13061,22 +13061,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场</t>
+          <t>华为智能生活馆•烟台龙口保利</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场城市展厅1号门</t>
+          <t>华为授权体验店（龙口保利广场）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13125,22 +13125,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>小米汽车四川省绵阳市涪城区万达广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（济南新辰天地）</t>
+          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13150,29 +13150,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>华为授权体验店（济南新辰天地）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -13194,17 +13194,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区万达广场</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市集美区集美汽车城</t>
+          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市集美区天水路503号</t>
+          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
+          <t>小米汽车福建省厦门市集美区集美汽车城</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
+          <t>福建省厦门市集美区天水路503号</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12522,17 +12522,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
         </is>
       </c>
     </row>
@@ -12554,17 +12554,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
+          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
         </is>
       </c>
     </row>
@@ -12591,12 +12591,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12606,29 +12606,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
+          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
+          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
         </is>
       </c>
     </row>
@@ -12650,17 +12650,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12670,29 +12670,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
+          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12702,29 +12702,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12734,29 +12734,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
+          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12766,14 +12766,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -12783,12 +12783,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12798,29 +12798,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12830,29 +12830,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
+          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12862,29 +12862,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
+          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12894,29 +12894,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
+          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
+          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
         </is>
       </c>
     </row>
@@ -12965,22 +12965,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>马鞍山雨山万达广场</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江九瑞大道销售服务中心</t>
+          <t>马鞍山雨山万达广场城市展厅1号门</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12997,22 +12997,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场</t>
+          <t>华为智能生活馆•烟台龙口保利</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场城市展厅1号门</t>
+          <t>华为授权体验店（龙口保利广场）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13061,22 +13061,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台龙口保利</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（龙口保利广场）</t>
+          <t>小鹏汽车九江九瑞大道销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13098,17 +13098,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13118,29 +13118,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区万达广场</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
+          <t>华为授权体验店（济南新辰天地）</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13150,14 +13150,14 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -13167,12 +13167,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（济南新辰天地）</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13194,17 +13194,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区万达广场</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
+          <t>小米汽车福建省厦门市集美区集美汽车城</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
+          <t>福建省厦门市集美区天水路503号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市集美区集美汽车城</t>
+          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市集美区天水路503号</t>
+          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司河西分公司</t>
+          <t>南京利之星汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -11939,12 +11939,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>鼓楼区汉中门大街309号B栋一层</t>
+          <t>栖霞区仙尧路9号</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期</t>
+          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司</t>
+          <t>南京利之星汽车销售服务有限公司河西分公司</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11971,12 +11971,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>栖霞区仙尧路9号</t>
+          <t>鼓楼区汉中门大街309号B栋一层</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 17 期</t>
         </is>
       </c>
     </row>
@@ -12485,22 +12485,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
+          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
         </is>
       </c>
     </row>
@@ -12549,22 +12549,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
+          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
         </is>
       </c>
     </row>
@@ -12591,12 +12591,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12606,29 +12606,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
+          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12638,29 +12638,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
+          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12670,14 +12670,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
+          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -12687,12 +12687,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
@@ -12714,17 +12714,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
+          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
         </is>
       </c>
     </row>
@@ -12746,17 +12746,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12766,29 +12766,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
@@ -12847,12 +12847,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12862,29 +12862,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
+          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12894,29 +12894,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
+          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
@@ -13029,22 +13029,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
+          <t>小鹏汽车九江九瑞大道销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13061,22 +13061,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江九瑞大道销售服务中心</t>
+          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13093,22 +13093,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>华为授权体验店（济南新辰天地）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13118,29 +13118,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（济南新辰天地）</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -13162,17 +13162,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车四川省绵阳市涪城区万达广场</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
@@ -13194,17 +13194,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区万达广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -10782,7 +10782,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
+          <t>小米汽车河北省保定市定州市保定定州万达</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
+          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市定州市保定定州万达</t>
+          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
+          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市集美区集美汽车城</t>
+          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市集美区天水路503号</t>
+          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
+          <t>小米汽车福建省厦门市集美区集美汽车城</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
+          <t>福建省厦门市集美区天水路503号</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司</t>
+          <t>南京利之星汽车销售服务有限公司河西分公司</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -11939,12 +11939,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>栖霞区仙尧路9号</t>
+          <t>鼓楼区汉中门大街309号B栋一层</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 17 期</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司河西分公司</t>
+          <t>南京利之星汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11971,12 +11971,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>鼓楼区汉中门大街309号B栋一层</t>
+          <t>栖霞区仙尧路9号</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期</t>
+          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12485,22 +12485,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
+          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
         </is>
       </c>
     </row>
@@ -12522,17 +12522,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12542,29 +12542,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
+          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12574,29 +12574,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
+          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
@@ -12645,22 +12645,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12670,29 +12670,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
+          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12702,29 +12702,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
+          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
         </is>
       </c>
     </row>
@@ -12746,17 +12746,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12766,29 +12766,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12798,29 +12798,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12830,14 +12830,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
+          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -12847,12 +12847,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
+          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
         </is>
       </c>
     </row>
@@ -12874,17 +12874,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12894,29 +12894,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
         </is>
       </c>
     </row>
@@ -12965,22 +12965,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场城市展厅1号门</t>
+          <t>小鹏汽车九江九瑞大道销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13029,22 +13029,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江九瑞大道销售服务中心</t>
+          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13061,22 +13061,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>马鞍山雨山万达广场</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
+          <t>马鞍山雨山万达广场城市展厅1号门</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13093,22 +13093,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（济南新辰天地）</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -13130,17 +13130,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>华为授权体验店（济南新辰天地）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E435"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
@@ -4323,14 +4323,14 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>0</v>
@@ -4344,14 +4344,14 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>0</v>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
@@ -4381,19 +4381,19 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>0</v>
@@ -4407,14 +4407,14 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>0</v>
@@ -4428,14 +4428,14 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E168" s="2" t="n">
         <v>0</v>
@@ -4449,14 +4449,14 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E169" s="2" t="n">
         <v>0</v>
@@ -4470,14 +4470,14 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E170" s="2" t="n">
         <v>0</v>
@@ -4491,14 +4491,14 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="E171" s="2" t="n">
         <v>0</v>
@@ -4512,14 +4512,14 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>0</v>
@@ -4533,14 +4533,14 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E173" s="2" t="n">
         <v>0</v>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E174" s="2" t="n">
         <v>0</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>0</v>
@@ -4596,14 +4596,14 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>0</v>
@@ -4617,14 +4617,14 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E177" s="2" t="n">
         <v>0</v>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E178" s="2" t="n">
         <v>0</v>
@@ -4659,38 +4659,38 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C179" s="2" t="n">
+      <c r="C180" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D179" s="2" t="n">
+      <c r="D180" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E179" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="D180" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="E180" s="4" t="n">
-        <v>1</v>
+      <c r="E180" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -4701,14 +4701,14 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E181" s="4" t="n">
         <v>1</v>
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E182" s="4" t="n">
         <v>1</v>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E183" s="4" t="n">
         <v>1</v>
@@ -4764,14 +4764,14 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E184" s="4" t="n">
         <v>1</v>
@@ -4785,14 +4785,14 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="E185" s="4" t="n">
         <v>1</v>
@@ -4806,14 +4806,14 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E186" s="4" t="n">
         <v>1</v>
@@ -4827,14 +4827,14 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="E187" s="4" t="n">
         <v>1</v>
@@ -4848,14 +4848,14 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="E188" s="4" t="n">
         <v>1</v>
@@ -4869,17 +4869,17 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -4890,14 +4890,14 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="E190" s="4" t="n">
         <v>2</v>
@@ -4911,14 +4911,14 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="E191" s="4" t="n">
         <v>2</v>
@@ -4932,14 +4932,14 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="E192" s="4" t="n">
         <v>2</v>
@@ -4953,17 +4953,17 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
@@ -4974,14 +4974,14 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="E194" s="4" t="n">
         <v>3</v>
@@ -4995,14 +4995,14 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="E195" s="4" t="n">
         <v>3</v>
@@ -5016,59 +5016,59 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="E196" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="inlineStr">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D197" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E197" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t>小鹏</t>
         </is>
       </c>
-      <c r="B197" s="3" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
         <is>
           <t>广东</t>
         </is>
       </c>
-      <c r="C197" s="3" t="n">
+      <c r="C198" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="D197" s="3" t="n">
+      <c r="D198" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="E197" s="3" t="n">
+      <c r="E198" s="3" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D198" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="E198" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -5079,14 +5079,14 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E199" s="2" t="n">
         <v>0</v>
@@ -5100,14 +5100,14 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>0</v>
@@ -5121,14 +5121,14 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>0</v>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>0</v>
@@ -5163,14 +5163,14 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="E203" s="2" t="n">
         <v>0</v>
@@ -5184,14 +5184,14 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E204" s="2" t="n">
         <v>0</v>
@@ -5205,14 +5205,14 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E205" s="2" t="n">
         <v>0</v>
@@ -5226,14 +5226,14 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>0</v>
@@ -5247,14 +5247,14 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>0</v>
@@ -5268,14 +5268,14 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>0</v>
@@ -5289,14 +5289,14 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E209" s="2" t="n">
         <v>0</v>
@@ -5310,14 +5310,14 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>0</v>
@@ -5331,14 +5331,14 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E211" s="2" t="n">
         <v>0</v>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>0</v>
@@ -5373,14 +5373,14 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>0</v>
@@ -5394,14 +5394,14 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>0</v>
@@ -5415,14 +5415,14 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E215" s="2" t="n">
         <v>0</v>
@@ -5436,14 +5436,14 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E216" s="2" t="n">
         <v>0</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>0</v>
@@ -5478,14 +5478,14 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>0</v>
@@ -5499,14 +5499,14 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>0</v>
@@ -5520,14 +5520,14 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>0</v>
@@ -5541,14 +5541,14 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E221" s="2" t="n">
         <v>0</v>
@@ -5562,14 +5562,14 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>0</v>
@@ -5583,14 +5583,14 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E223" s="2" t="n">
         <v>0</v>
@@ -5604,38 +5604,38 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C224" s="2" t="n">
+      <c r="C225" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D224" s="2" t="n">
+      <c r="D225" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E224" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="4" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B225" s="4" t="inlineStr">
-        <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D225" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E225" s="4" t="n">
-        <v>1</v>
+      <c r="E225" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -5646,38 +5646,38 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D226" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E226" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
           <t>江苏</t>
         </is>
       </c>
-      <c r="C226" s="4" t="n">
+      <c r="C227" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="D226" s="4" t="n">
+      <c r="D227" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="E226" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D227" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E227" s="2" t="n">
-        <v>0</v>
+      <c r="E227" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="228">
@@ -5688,14 +5688,14 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C228" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E228" s="2" t="n">
         <v>0</v>
@@ -5709,14 +5709,14 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C229" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E229" s="2" t="n">
         <v>0</v>
@@ -5730,14 +5730,14 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C230" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E230" s="2" t="n">
         <v>0</v>
@@ -5751,14 +5751,14 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E231" s="2" t="n">
         <v>0</v>
@@ -5772,14 +5772,14 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E232" s="2" t="n">
         <v>0</v>
@@ -5793,14 +5793,14 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E233" s="2" t="n">
         <v>0</v>
@@ -5814,14 +5814,14 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C234" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E234" s="2" t="n">
         <v>0</v>
@@ -5835,14 +5835,14 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E235" s="2" t="n">
         <v>0</v>
@@ -5856,14 +5856,14 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E236" s="2" t="n">
         <v>0</v>
@@ -5877,14 +5877,14 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E237" s="2" t="n">
         <v>0</v>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C238" s="2" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D238" s="2" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E238" s="2" t="n">
         <v>0</v>
@@ -5919,14 +5919,14 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E239" s="2" t="n">
         <v>0</v>
@@ -5940,14 +5940,14 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C240" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E240" s="2" t="n">
         <v>0</v>
@@ -5961,14 +5961,14 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C241" s="2" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D241" s="2" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E241" s="2" t="n">
         <v>0</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C242" s="2" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D242" s="2" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E242" s="2" t="n">
         <v>0</v>
@@ -6003,14 +6003,14 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C243" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E243" s="2" t="n">
         <v>0</v>
@@ -6024,14 +6024,14 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C244" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D244" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E244" s="2" t="n">
         <v>0</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C245" s="2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E245" s="2" t="n">
         <v>0</v>
@@ -6066,14 +6066,14 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C246" s="2" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E246" s="2" t="n">
         <v>0</v>
@@ -6087,14 +6087,14 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C247" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E247" s="2" t="n">
         <v>0</v>
@@ -6108,14 +6108,14 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C248" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D248" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E248" s="2" t="n">
         <v>0</v>
@@ -6129,14 +6129,14 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C249" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E249" s="2" t="n">
         <v>0</v>
@@ -6150,14 +6150,14 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C250" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E250" s="2" t="n">
         <v>0</v>
@@ -6171,14 +6171,14 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C251" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E251" s="2" t="n">
         <v>0</v>
@@ -6192,14 +6192,14 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C252" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E252" s="2" t="n">
         <v>0</v>
@@ -6213,14 +6213,14 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C253" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E253" s="2" t="n">
         <v>0</v>
@@ -6234,14 +6234,14 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C254" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D254" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E254" s="2" t="n">
         <v>0</v>
@@ -6255,14 +6255,14 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C255" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D255" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E255" s="2" t="n">
         <v>0</v>
@@ -6276,14 +6276,14 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C256" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D256" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E256" s="2" t="n">
         <v>0</v>
@@ -6297,14 +6297,14 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C257" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D257" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E257" s="2" t="n">
         <v>0</v>
@@ -6313,19 +6313,19 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C258" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D258" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E258" s="2" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C259" s="2" t="n">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C260" s="2" t="n">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C261" s="2" t="n">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C262" s="2" t="n">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C263" s="2" t="n">
@@ -6444,14 +6444,14 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C264" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D264" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E264" s="2" t="n">
         <v>0</v>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C265" s="2" t="n">
@@ -6486,14 +6486,14 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C266" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E266" s="2" t="n">
         <v>0</v>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="2" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="2" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="2" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="2" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="2" t="n">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C272" s="2" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C273" s="2" t="n">
@@ -6649,19 +6649,19 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C274" s="2" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D274" s="2" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="E274" s="2" t="n">
         <v>0</v>
@@ -6675,14 +6675,14 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C275" s="2" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E275" s="2" t="n">
         <v>0</v>
@@ -6696,14 +6696,14 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C276" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E276" s="2" t="n">
         <v>0</v>
@@ -6717,14 +6717,14 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C277" s="2" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E277" s="2" t="n">
         <v>0</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C278" s="2" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E278" s="2" t="n">
         <v>0</v>
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C279" s="2" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="E279" s="2" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C280" s="2" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E280" s="2" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C281" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E281" s="2" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E282" s="2" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E283" s="2" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="E284" s="2" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E285" s="2" t="n">
         <v>0</v>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C286" s="2" t="n">
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E287" s="2" t="n">
         <v>0</v>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C288" s="2" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E288" s="2" t="n">
         <v>0</v>
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E289" s="2" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E290" s="2" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E291" s="2" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E292" s="2" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E293" s="2" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C294" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E294" s="2" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E295" s="2" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E296" s="2" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E297" s="2" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C298" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E298" s="2" t="n">
         <v>0</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C299" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E299" s="2" t="n">
         <v>0</v>
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C300" s="2" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D300" s="2" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E300" s="2" t="n">
         <v>0</v>
@@ -7221,38 +7221,38 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D301" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C301" s="2" t="n">
+      <c r="C302" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D301" s="2" t="n">
+      <c r="D302" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E301" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B302" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C302" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="D302" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="E302" s="4" t="n">
-        <v>1</v>
+      <c r="E302" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -7263,14 +7263,14 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C303" s="4" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D303" s="4" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E303" s="4" t="n">
         <v>1</v>
@@ -7284,38 +7284,38 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="D304" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="E304" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
           <t>福建</t>
         </is>
       </c>
-      <c r="C304" s="4" t="n">
+      <c r="C305" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D304" s="4" t="n">
+      <c r="D305" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E304" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B305" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C305" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D305" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="E305" s="2" t="n">
-        <v>0</v>
+      <c r="E305" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E306" s="2" t="n">
         <v>0</v>
@@ -7347,14 +7347,14 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E307" s="2" t="n">
         <v>0</v>
@@ -7368,14 +7368,14 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C308" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E308" s="2" t="n">
         <v>0</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E309" s="2" t="n">
         <v>0</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E310" s="2" t="n">
         <v>0</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E311" s="2" t="n">
         <v>0</v>
@@ -7452,14 +7452,14 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E312" s="2" t="n">
         <v>0</v>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C313" s="2" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="E313" s="2" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C314" s="2" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="E314" s="2" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="E315" s="2" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="E316" s="2" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="E317" s="2" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E318" s="2" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="E319" s="2" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="E320" s="2" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="E321" s="2" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E322" s="2" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="E323" s="2" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="E324" s="2" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C325" s="2" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E325" s="2" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C326" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E326" s="2" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C327" s="2" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E327" s="2" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C328" s="2" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E328" s="2" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E329" s="2" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C330" s="2" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E330" s="2" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E331" s="2" t="n">
         <v>0</v>
@@ -7872,14 +7872,14 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C332" s="2" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E332" s="2" t="n">
         <v>0</v>
@@ -7893,14 +7893,14 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C333" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E333" s="2" t="n">
         <v>0</v>
@@ -7914,14 +7914,14 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C334" s="2" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E334" s="2" t="n">
         <v>0</v>
@@ -7935,38 +7935,38 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D335" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C335" s="2" t="n">
+      <c r="C336" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D335" s="2" t="n">
+      <c r="D336" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E335" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="3" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C336" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="D336" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="E336" s="3" t="n">
-        <v>-1</v>
+      <c r="E336" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -7977,14 +7977,14 @@
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D337" s="3" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E337" s="3" t="n">
         <v>-1</v>
@@ -7998,38 +7998,38 @@
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="D338" s="3" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="E338" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="inlineStr">
+      <c r="A339" s="3" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B339" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C339" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="D339" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="E339" s="2" t="n">
-        <v>0</v>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D339" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="340">
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E343" s="2" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D346" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E346" s="2" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="E349" s="2" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C351" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E351" s="2" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C353" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E353" s="2" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C354" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E354" s="2" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C355" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E355" s="2" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E356" s="2" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D357" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E357" s="2" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C358" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E358" s="2" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C359" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E359" s="2" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C360" s="2" t="n">
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>0</v>
@@ -8502,38 +8502,38 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D362" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E362" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C362" s="2" t="n">
+      <c r="C363" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D362" s="2" t="n">
+      <c r="D363" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E362" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="4" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B363" s="4" t="inlineStr">
-        <is>
-          <t>天津</t>
-        </is>
-      </c>
-      <c r="C363" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D363" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E363" s="4" t="n">
-        <v>1</v>
+      <c r="E363" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -8544,14 +8544,14 @@
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C364" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D364" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E364" s="4" t="n">
         <v>1</v>
@@ -8565,38 +8565,38 @@
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D365" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E365" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="4" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B366" s="4" t="inlineStr">
+        <is>
           <t>贵州</t>
         </is>
       </c>
-      <c r="C365" s="4" t="n">
+      <c r="C366" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D365" s="4" t="n">
+      <c r="D366" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E365" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="2" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B366" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C366" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D366" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E366" s="2" t="n">
-        <v>0</v>
+      <c r="E366" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="367">
@@ -8607,14 +8607,14 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D367" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E367" s="2" t="n">
         <v>0</v>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
@@ -8649,14 +8649,14 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D369" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E369" s="2" t="n">
         <v>0</v>
@@ -8670,14 +8670,14 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D370" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E370" s="2" t="n">
         <v>0</v>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
@@ -8712,14 +8712,14 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C372" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D372" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E372" s="2" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C373" s="2" t="n">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
@@ -8770,19 +8770,19 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C375" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D375" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E375" s="2" t="n">
         <v>0</v>
@@ -8796,14 +8796,14 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C376" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D376" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E376" s="2" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C377" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D377" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E377" s="2" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E378" s="2" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E379" s="2" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E380" s="2" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E381" s="2" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E382" s="2" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C383" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D383" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E383" s="2" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C384" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D384" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E384" s="2" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C385" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D385" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E385" s="2" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C386" s="2" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D386" s="2" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E386" s="2" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C387" s="2" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D387" s="2" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E387" s="2" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C388" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E388" s="2" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D389" s="2" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E389" s="2" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C390" s="2" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D390" s="2" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E390" s="2" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C391" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D391" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E391" s="2" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C392" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D392" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E392" s="2" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C393" s="2" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D393" s="2" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C394" s="2" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D394" s="2" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E394" s="2" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C395" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D395" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E395" s="2" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C396" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D396" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E396" s="2" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C397" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D397" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E397" s="2" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D398" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E398" s="2" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C399" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D399" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E399" s="2" t="n">
         <v>0</v>
@@ -9300,14 +9300,14 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C400" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D400" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E400" s="2" t="n">
         <v>0</v>
@@ -9321,14 +9321,14 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C401" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D401" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E401" s="2" t="n">
         <v>0</v>
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D402" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E402" s="2" t="n">
         <v>0</v>
@@ -9363,14 +9363,14 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C403" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D403" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E403" s="2" t="n">
         <v>0</v>
@@ -9384,38 +9384,38 @@
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C404" s="2" t="n">
+      <c r="C405" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D404" s="2" t="n">
+      <c r="D405" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E404" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="3" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C405" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="D405" s="3" t="n">
-        <v>124</v>
-      </c>
-      <c r="E405" s="3" t="n">
-        <v>-2</v>
+      <c r="E405" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -9426,38 +9426,38 @@
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C406" s="3" t="n">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="D406" s="3" t="n">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="E406" s="3" t="n">
         <v>-2</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="inlineStr">
+      <c r="A407" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B407" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C407" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="D407" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="E407" s="2" t="n">
-        <v>0</v>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C407" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D407" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="408">
@@ -9468,14 +9468,14 @@
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C408" s="2" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D408" s="2" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E408" s="2" t="n">
         <v>0</v>
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D409" s="2" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>0</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="D410" s="2" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="E410" s="2" t="n">
         <v>0</v>
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D411" s="2" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="E411" s="2" t="n">
         <v>0</v>
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D412" s="2" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E412" s="2" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>183</v>
+        <v>34</v>
       </c>
       <c r="D413" s="2" t="n">
-        <v>183</v>
+        <v>34</v>
       </c>
       <c r="E413" s="2" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>33</v>
+        <v>183</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>33</v>
+        <v>183</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D420" s="2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D426" s="2" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>0</v>
@@ -9867,38 +9867,38 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D427" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C427" s="2" t="n">
+      <c r="C428" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D427" s="2" t="n">
+      <c r="D428" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E427" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B428" s="4" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C428" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="D428" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="E428" s="4" t="n">
-        <v>1</v>
+      <c r="E428" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="429">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C429" s="4" t="n">
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C430" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D430" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E430" s="4" t="n">
         <v>1</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C431" s="4" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D431" s="4" t="n">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="E431" s="4" t="n">
         <v>1</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>1</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="E433" s="4" t="n">
         <v>1</v>
@@ -10014,17 +10014,17 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C434" s="4" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D434" s="4" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E434" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -10035,16 +10035,37 @@
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="D435" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="E435" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C435" s="4" t="n">
+      <c r="C436" s="4" t="n">
         <v>141</v>
       </c>
-      <c r="D435" s="4" t="n">
+      <c r="D436" s="4" t="n">
         <v>143</v>
       </c>
-      <c r="E435" s="4" t="n">
+      <c r="E436" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10782,7 +10803,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市定州市保定定州万达</t>
+          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10797,7 +10818,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
+          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10814,7 +10835,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
+          <t>小米汽车河北省保定市定州市保定定州万达</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -10829,7 +10850,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
+          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -11924,7 +11945,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司河西分公司</t>
+          <t>南京利之星汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -11939,12 +11960,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>鼓楼区汉中门大街309号B栋一层</t>
+          <t>栖霞区仙尧路9号</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期</t>
+          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11977,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司</t>
+          <t>南京利之星汽车销售服务有限公司河西分公司</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11971,12 +11992,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>栖霞区仙尧路9号</t>
+          <t>鼓楼区汉中门大街309号B栋一层</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 17 期</t>
         </is>
       </c>
     </row>
@@ -12522,17 +12543,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12542,7 +12563,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
@@ -12554,17 +12575,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12574,14 +12595,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
+          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -12591,12 +12612,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12606,29 +12627,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12638,7 +12659,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
@@ -12650,17 +12671,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12670,29 +12691,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
+          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12702,29 +12723,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
+          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12734,7 +12755,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
+          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
         </is>
       </c>
     </row>
@@ -12746,17 +12767,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12766,29 +12787,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12798,7 +12819,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
+          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
         </is>
       </c>
     </row>
@@ -12810,17 +12831,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12830,29 +12851,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
+          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12862,29 +12883,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
+          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12894,29 +12915,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12926,7 +12947,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
+          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
         </is>
       </c>
     </row>
@@ -12965,22 +12986,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>马鞍山雨山万达广场</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江九瑞大道销售服务中心</t>
+          <t>马鞍山雨山万达广场城市展厅1号门</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13061,22 +13082,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场城市展厅1号门</t>
+          <t>小鹏汽车九江九瑞大道销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13093,22 +13114,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>华为授权体验店（济南新辰天地）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13118,7 +13139,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -13130,17 +13151,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车四川省绵阳市涪城区万达广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13150,7 +13171,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
@@ -13162,17 +13183,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区万达广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13182,29 +13203,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（济南新辰天地）</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13214,7 +13235,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -11945,7 +11945,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司</t>
+          <t>南京利之星汽车销售服务有限公司河西分公司</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -11960,12 +11960,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>栖霞区仙尧路9号</t>
+          <t>鼓楼区汉中门大街309号B栋一层</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 17 期</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司河西分公司</t>
+          <t>南京利之星汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>鼓楼区汉中门大街309号B栋一层</t>
+          <t>栖霞区仙尧路9号</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期</t>
+          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12506,22 +12506,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12531,29 +12531,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
+          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
         </is>
       </c>
     </row>
@@ -12575,17 +12575,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
@@ -12607,17 +12607,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
         </is>
       </c>
     </row>
@@ -12639,17 +12639,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12659,29 +12659,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12691,14 +12691,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12723,29 +12723,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
+          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
+          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
         </is>
       </c>
     </row>
@@ -12767,17 +12767,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
+          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
         </is>
       </c>
     </row>
@@ -12858,22 +12858,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12883,29 +12883,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
+          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
         </is>
       </c>
     </row>
@@ -12986,22 +12986,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场城市展厅1号门</t>
+          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13018,22 +13018,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台龙口保利</t>
+          <t>马鞍山雨山万达广场</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（龙口保利广场）</t>
+          <t>马鞍山雨山万达广场城市展厅1号门</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13050,22 +13050,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
+          <t>小鹏汽车九江九瑞大道销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13082,22 +13082,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>华为智能生活馆•烟台龙口保利</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江九瑞大道销售服务中心</t>
+          <t>华为授权体验店（龙口保利广场）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13114,7 +13114,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -13124,12 +13124,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（济南新辰天地）</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13139,29 +13139,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区万达广场</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
+          <t>华为授权体验店（济南新辰天地）</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -13183,17 +13183,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -13215,17 +13215,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区万达广场</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
+          <t>小米汽车河北省保定市定州市保定定州万达</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
+          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市定州市保定定州万达</t>
+          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
+          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
+          <t>小米汽车福建省厦门市集美区集美汽车城</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
+          <t>福建省厦门市集美区天水路503号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市集美区集美汽车城</t>
+          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市集美区天水路503号</t>
+          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司河西分公司</t>
+          <t>南京利之星汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -11960,12 +11960,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>鼓楼区汉中门大街309号B栋一层</t>
+          <t>栖霞区仙尧路9号</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期</t>
+          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司</t>
+          <t>南京利之星汽车销售服务有限公司河西分公司</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>栖霞区仙尧路9号</t>
+          <t>鼓楼区汉中门大街309号B栋一层</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 17 期</t>
         </is>
       </c>
     </row>
@@ -12511,17 +12511,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12531,29 +12531,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
+          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12563,29 +12563,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
+          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12595,29 +12595,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12627,29 +12627,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
+          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12659,29 +12659,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
+          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12691,29 +12691,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12723,29 +12723,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
+          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
         </is>
       </c>
     </row>
@@ -12767,17 +12767,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12787,29 +12787,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
+          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
+          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
         </is>
       </c>
     </row>
@@ -12831,17 +12831,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
+          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
         </is>
       </c>
     </row>
@@ -12863,17 +12863,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12883,29 +12883,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12915,29 +12915,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
+          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
@@ -12986,22 +12986,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
+          <t>小鹏汽车九江九瑞大道销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13050,22 +13050,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江九瑞大道销售服务中心</t>
+          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13119,17 +13119,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13139,29 +13139,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>小米汽车四川省绵阳市涪城区万达广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（济南新辰天地）</t>
+          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>华为授权体验店（济南新辰天地）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -13215,17 +13215,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区万达广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵阳涪城万达</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市定州市保定定州万达</t>
+          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
+          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河北省保定市容城县保定雄安易安邻里中心</t>
+          <t>小米汽车河北省保定市定州市保定定州万达</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>河北省保定市容城县博远路86号雄安易安邻里中心1F</t>
+          <t>定州市北城街道迎宾大道和北门街交叉口东南角万达广场</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市集美区集美汽车城</t>
+          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市集美区天水路503号</t>
+          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市湖里区厦门SM城市广场三期</t>
+          <t>小米汽车福建省厦门市集美区集美汽车城</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>福建省厦门市湖里区SM城市广场三期1层近中庭</t>
+          <t>福建省厦门市集美区天水路503号</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司</t>
+          <t>南京利之星汽车销售服务有限公司河西分公司</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -11960,12 +11960,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>栖霞区仙尧路9号</t>
+          <t>鼓楼区汉中门大街309号B栋一层</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 17 期</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>南京利之星汽车销售服务有限公司河西分公司</t>
+          <t>南京利之星汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>鼓楼区汉中门大街309号B栋一层</t>
+          <t>栖霞区仙尧路9号</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>连续在档 17 期</t>
+          <t>连续在档 17 期；本期存在高相似店名「福州利之星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12511,17 +12511,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>小鹏汽车潍坊渤海路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12531,14 +12531,14 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
+          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -12548,12 +12548,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12563,29 +12563,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
+          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12595,29 +12595,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12627,29 +12627,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
+          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12659,29 +12659,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
+          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12691,29 +12691,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12723,29 +12723,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊渤海路销售服务中心</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市寒亭区通亭街6369号 → 山东省潍坊市寒亭区开元街道通亭街6369号202号</t>
+          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
         </is>
       </c>
     </row>
@@ -12767,17 +12767,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
@@ -12799,17 +12799,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12819,29 +12819,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
+          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12851,29 +12851,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
+          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12883,29 +12883,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
+          <t>河北省沧州市开发区石港路71号 → 河北省沧州市开发区黄河路与石岗路交叉口路北</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12915,29 +12915,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
+          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
         </is>
       </c>
     </row>
@@ -13114,22 +13114,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>华为授权体验店（济南新辰天地）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -13178,7 +13178,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（济南新辰天地）</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13215,17 +13215,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260824_vs_20260831.xlsx
@@ -12538,22 +12538,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12563,29 +12563,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
+          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 襄阳光彩</t>
+          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12595,29 +12595,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
+          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12627,29 +12627,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
+          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海环宇城</t>
+          <t>Bentley Xiamen</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12659,29 +12659,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
+          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省恩施市恩施和润城</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12691,29 +12691,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
+          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Bentley Xiamen</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Room 107 113, 1/F, No.88  Shuangshi West Road → Unit 10, 1F, Podium Block Guojin Plaza, No. 506-508</t>
+          <t>汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧） → 汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号</t>
         </is>
       </c>
     </row>
@@ -12735,17 +12735,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省衢州市龙游县龙游银泰</t>
+          <t>小米汽车湖北省恩施市恩施和润城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>龙游县龙洲街道兴龙南路45号 → 浙江省衢州市龙游县兴龙南路45号</t>
+          <t>湖北省恩施土家族苗族自治州恩施市和润城A馆中庭 → 湖北省恩施土家族苗族自治州恩施市和润城B馆中庭</t>
         </is>
       </c>
     </row>
@@ -12767,17 +12767,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12787,29 +12787,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>安徽省安庆市英德利国际汽车城福旺路 → 安庆市英德利国际汽车城松祥路与福旺路交叉口北60米</t>
+          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆金菱车世界销售服务中心</t>
+          <t>上汽奥迪天津奥兴用户中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12819,29 +12819,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆经开区白鹤路工业园区1号 → 重庆市南岸区经开区白鹤路工业园1号（附9号）</t>
+          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>蔚来空间 | 珠海环宇城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650103 → 日新东路259号 西山区 650228</t>
+          <t>广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115 → 广东省珠海市香洲区前河北路 96 号珠海环宇城L1-115、LL6</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省泰安市岱岳区泰山国际汽车城</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12915,29 +12915,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省泰安市泰山国际汽车城山东临工（泰东路） → 秦东路202号</t>
+          <t>山东省东营市垦利区董集镇北二路14号 → 山东省东营市垦利区董集镇北二路5号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪天津奥兴用户中心</t>
+          <t>蔚来体验中心 | 襄阳光彩</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>双街镇京津公路东侧双江道南庞大汽贸园内21号 → 天津市双街镇京津公路双江道南庞大汽贸园21号</t>
+          <t>湖北省襄阳市襄州区钻石大道28号 → 襄州区钻石大道与西湾路交叉口东北120米</t>
         </is>
       </c>
     </row>
@@ -12986,22 +12986,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江九瑞大道销售服务中心</t>
+          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13018,22 +13018,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>马鞍山雨山万达广场城市展厅1号门</t>
+          <t>小鹏汽车九江九瑞大道销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13050,22 +13050,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>华为智能生活馆•烟台龙口保利</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市海曙区汽车园区</t>
+          <t>华为授权体验店（龙口保利广场）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13082,22 +13082,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台龙口保利</t>
+          <t>马鞍山雨山万达广场</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（龙口保利广场）</t>
+          <t>马鞍山雨山万达广场城市展厅1号门</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
